--- a/2-OI_a/Campagnes.xlsx
+++ b/2-OI_a/Campagnes.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F166"/>
+  <dimension ref="A1:F155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -730,7 +730,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -763,3334 +763,3092 @@
         <v>42156</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="E15" t="n">
-        <v>50540.5</v>
+        <v>62209.5</v>
       </c>
       <c r="F15" t="n">
-        <v>1049590.319046441</v>
+        <v>1050009.436781199</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15-06</t>
+          <t>15-07</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>42156</v>
+        <v>42186</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>81</v>
       </c>
       <c r="E16" t="n">
-        <v>11669</v>
+        <v>86006</v>
       </c>
       <c r="F16" t="n">
-        <v>1051824.709715771</v>
+        <v>1048031.045520041</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>15-07</t>
+          <t>15-09</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>42186</v>
+        <v>42248</v>
       </c>
       <c r="D17" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E17" t="n">
-        <v>86006</v>
+        <v>88736.5</v>
       </c>
       <c r="F17" t="n">
-        <v>1048031.045520041</v>
+        <v>1041917.550274136</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>15-09</t>
+          <t>15-10</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>42248</v>
+        <v>42278</v>
       </c>
       <c r="D18" t="n">
-        <v>86</v>
+        <v>166</v>
       </c>
       <c r="E18" t="n">
-        <v>88736.5</v>
+        <v>173272.5</v>
       </c>
       <c r="F18" t="n">
-        <v>1041917.550274136</v>
+        <v>1047900.540370524</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>15-10</t>
+          <t>15-11</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>42278</v>
+        <v>42309</v>
       </c>
       <c r="D19" t="n">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="E19" t="n">
-        <v>86786</v>
+        <v>57109.5</v>
       </c>
       <c r="F19" t="n">
-        <v>1039234.893673807</v>
+        <v>1045098.817396843</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15-10</t>
+          <t>15-12</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>42278</v>
+        <v>42339</v>
       </c>
       <c r="D20" t="n">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="E20" t="n">
-        <v>86486.5</v>
+        <v>52168</v>
       </c>
       <c r="F20" t="n">
-        <v>1056596.195926262</v>
+        <v>1036025.665251367</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15-11</t>
+          <t>15-12</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>42309</v>
+        <v>42339</v>
       </c>
       <c r="D21" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="E21" t="n">
-        <v>57109.5</v>
+        <v>46859.5</v>
       </c>
       <c r="F21" t="n">
-        <v>1045098.817396843</v>
+        <v>1040246.858471263</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>15-12</t>
+          <t>16-01</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>42339</v>
+        <v>42370</v>
       </c>
       <c r="D22" t="n">
-        <v>51</v>
+        <v>99</v>
       </c>
       <c r="E22" t="n">
-        <v>52168</v>
+        <v>105847.6666666667</v>
       </c>
       <c r="F22" t="n">
-        <v>1036025.665251367</v>
+        <v>1035697.085051712</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15-12</t>
+          <t>16-02</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>42339</v>
+        <v>42401</v>
       </c>
       <c r="D23" t="n">
-        <v>44</v>
+        <v>133</v>
       </c>
       <c r="E23" t="n">
-        <v>46859.5</v>
+        <v>142487.5</v>
       </c>
       <c r="F23" t="n">
-        <v>1040246.858471263</v>
+        <v>1034456.548567418</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16-01</t>
+          <t>16-03</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>42370</v>
+        <v>42430</v>
       </c>
       <c r="D24" t="n">
-        <v>99</v>
+        <v>130</v>
       </c>
       <c r="E24" t="n">
-        <v>105847.6666666667</v>
+        <v>139630.6666666667</v>
       </c>
       <c r="F24" t="n">
-        <v>1035697.085051712</v>
+        <v>1032455.833946459</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>16-02</t>
+          <t>16-04</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>42401</v>
+        <v>42461</v>
       </c>
       <c r="D25" t="n">
-        <v>133</v>
+        <v>74</v>
       </c>
       <c r="E25" t="n">
-        <v>142487.5</v>
+        <v>78629</v>
       </c>
       <c r="F25" t="n">
-        <v>1034456.548567418</v>
+        <v>1032568.220963851</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>16-03</t>
+          <t>16-05</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>42430</v>
+        <v>42491</v>
       </c>
       <c r="D26" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E26" t="n">
-        <v>67001.66666666667</v>
+        <v>58398</v>
       </c>
       <c r="F26" t="n">
-        <v>1034407.561788264</v>
+        <v>1035430.083341296</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>16-03</t>
+          <t>16-06</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>42430</v>
+        <v>42522</v>
       </c>
       <c r="D27" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="E27" t="n">
-        <v>72629</v>
+        <v>61103</v>
       </c>
       <c r="F27" t="n">
-        <v>1030655.327010102</v>
+        <v>1046800.157189186</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>16-04</t>
+          <t>16-07</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>42461</v>
+        <v>42552</v>
       </c>
       <c r="D28" t="n">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="E28" t="n">
-        <v>78629</v>
+        <v>48598</v>
       </c>
       <c r="F28" t="n">
-        <v>1032568.220963851</v>
+        <v>1053555.286732753</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>16-05</t>
+          <t>16-08</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>42491</v>
+        <v>42583</v>
       </c>
       <c r="D29" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="E29" t="n">
-        <v>58398</v>
+        <v>37976</v>
       </c>
       <c r="F29" t="n">
-        <v>1035430.083341296</v>
+        <v>1026246.039891971</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>16-06</t>
+          <t>16-09</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>42522</v>
+        <v>42614</v>
       </c>
       <c r="D30" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E30" t="n">
-        <v>61103</v>
+        <v>61754.5</v>
       </c>
       <c r="F30" t="n">
-        <v>1046800.157189186</v>
+        <v>1041154.725720433</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>16-07</t>
+          <t>16-09</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>42552</v>
+        <v>42614</v>
       </c>
       <c r="D31" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="E31" t="n">
-        <v>48598</v>
+        <v>60785</v>
       </c>
       <c r="F31" t="n">
-        <v>1053555.286732753</v>
+        <v>1038091.409063804</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>16-08</t>
+          <t>16-10</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>42583</v>
+        <v>42644</v>
       </c>
       <c r="D32" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E32" t="n">
-        <v>37976</v>
+        <v>40665.5</v>
       </c>
       <c r="F32" t="n">
-        <v>1026246.039891971</v>
+        <v>1047603.10242507</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>16-09</t>
+          <t>16-10</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>42614</v>
+        <v>42644</v>
       </c>
       <c r="D33" t="n">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="E33" t="n">
-        <v>61754.5</v>
+        <v>33960</v>
       </c>
       <c r="F33" t="n">
-        <v>1041154.725720433</v>
+        <v>1040187.617689782</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>16-09</t>
+          <t>16-11</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>42614</v>
+        <v>42675</v>
       </c>
       <c r="D34" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="E34" t="n">
-        <v>60785</v>
+        <v>37902.33333333334</v>
       </c>
       <c r="F34" t="n">
-        <v>1038091.409063804</v>
+        <v>1039695.534619966</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>16-10</t>
+          <t>16-11</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>42644</v>
+        <v>42675</v>
       </c>
       <c r="D35" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E35" t="n">
-        <v>40665.5</v>
+        <v>52201</v>
       </c>
       <c r="F35" t="n">
-        <v>1047603.10242507</v>
+        <v>1038124.221394482</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>16-10</t>
+          <t>16-12</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>42644</v>
+        <v>42705</v>
       </c>
       <c r="D36" t="n">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="E36" t="n">
-        <v>33960</v>
+        <v>119652.25</v>
       </c>
       <c r="F36" t="n">
-        <v>1040187.617689782</v>
+        <v>1037569.785878048</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>16-11</t>
+          <t>17-02</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>42675</v>
+        <v>42767</v>
       </c>
       <c r="D37" t="n">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="E37" t="n">
-        <v>37902.33333333334</v>
+        <v>90983.5</v>
       </c>
       <c r="F37" t="n">
-        <v>1039695.534619966</v>
+        <v>1042573.710930187</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>16-11</t>
+          <t>17-03</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>42675</v>
+        <v>42795</v>
       </c>
       <c r="D38" t="n">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="E38" t="n">
-        <v>52201</v>
+        <v>76783.66666666667</v>
       </c>
       <c r="F38" t="n">
-        <v>1038124.221394482</v>
+        <v>1033722.364997873</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>16-12</t>
+          <t>17-04</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>42705</v>
+        <v>42826</v>
       </c>
       <c r="D39" t="n">
-        <v>112</v>
+        <v>149</v>
       </c>
       <c r="E39" t="n">
-        <v>119652.25</v>
+        <v>162053.5</v>
       </c>
       <c r="F39" t="n">
-        <v>1037569.785878048</v>
+        <v>1045051.189817457</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>17-02</t>
+          <t>17-05</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>42767</v>
+        <v>42856</v>
       </c>
       <c r="D40" t="n">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="E40" t="n">
-        <v>90983.5</v>
+        <v>119738.6666666667</v>
       </c>
       <c r="F40" t="n">
-        <v>1042573.710930187</v>
+        <v>1038673.639532231</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>17-03</t>
+          <t>17-06</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>42795</v>
+        <v>42887</v>
       </c>
       <c r="D41" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E41" t="n">
-        <v>76783.66666666667</v>
+        <v>72159</v>
       </c>
       <c r="F41" t="n">
-        <v>1033722.364997873</v>
+        <v>1042503.776512054</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>17-04</t>
+          <t>17-08</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>42826</v>
+        <v>42948</v>
       </c>
       <c r="D42" t="n">
-        <v>149</v>
+        <v>105</v>
       </c>
       <c r="E42" t="n">
-        <v>162053.5</v>
+        <v>113281.5</v>
       </c>
       <c r="F42" t="n">
-        <v>1045051.189817457</v>
+        <v>1027334.540592859</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>17-05</t>
+          <t>17-09</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>42856</v>
+        <v>42979</v>
       </c>
       <c r="D43" t="n">
-        <v>111</v>
+        <v>10</v>
       </c>
       <c r="E43" t="n">
-        <v>119738.6666666667</v>
+        <v>10569.66666666667</v>
       </c>
       <c r="F43" t="n">
-        <v>1038673.639532231</v>
+        <v>1040699.291673237</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>17-06</t>
+          <t>17-09</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>42887</v>
+        <v>42979</v>
       </c>
       <c r="D44" t="n">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="E44" t="n">
-        <v>72159</v>
+        <v>47112</v>
       </c>
       <c r="F44" t="n">
-        <v>1042503.776512054</v>
+        <v>1047876.80242295</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>17-08</t>
+          <t>17-10</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>42948</v>
+        <v>43009</v>
       </c>
       <c r="D45" t="n">
-        <v>105</v>
+        <v>60</v>
       </c>
       <c r="E45" t="n">
-        <v>113281.5</v>
+        <v>61257</v>
       </c>
       <c r="F45" t="n">
-        <v>1027334.540592859</v>
+        <v>1046935.617922577</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>17-09</t>
+          <t>17-11</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>42979</v>
+        <v>43040</v>
       </c>
       <c r="D46" t="n">
-        <v>10</v>
+        <v>109</v>
       </c>
       <c r="E46" t="n">
-        <v>10569.66666666667</v>
+        <v>114179</v>
       </c>
       <c r="F46" t="n">
-        <v>1040699.291673237</v>
+        <v>1033649.831424489</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>17-09</t>
+          <t>17-12</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>42979</v>
+        <v>43070</v>
       </c>
       <c r="D47" t="n">
-        <v>46</v>
+        <v>99</v>
       </c>
       <c r="E47" t="n">
-        <v>47112</v>
+        <v>102672.5</v>
       </c>
       <c r="F47" t="n">
-        <v>1047876.80242295</v>
+        <v>1028984.19102689</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>17-10</t>
+          <t>18-01</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>43009</v>
+        <v>43101</v>
       </c>
       <c r="D48" t="n">
         <v>60</v>
       </c>
       <c r="E48" t="n">
-        <v>61257</v>
+        <v>61323</v>
       </c>
       <c r="F48" t="n">
-        <v>1046935.617922577</v>
+        <v>1052124.507172404</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>17-11</t>
+          <t>18-02</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>43040</v>
+        <v>43132</v>
       </c>
       <c r="D49" t="n">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="E49" t="n">
-        <v>114179</v>
+        <v>91242.5</v>
       </c>
       <c r="F49" t="n">
-        <v>1033649.831424489</v>
+        <v>1052829.922652547</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>17-12</t>
+          <t>18-07</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>43070</v>
+        <v>43282</v>
       </c>
       <c r="D50" t="n">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="E50" t="n">
-        <v>102672.5</v>
+        <v>119044.5</v>
       </c>
       <c r="F50" t="n">
-        <v>1028984.19102689</v>
+        <v>1031020.024357838</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>18-01</t>
+          <t>18-08</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>43101</v>
+        <v>43313</v>
       </c>
       <c r="D51" t="n">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="E51" t="n">
-        <v>61323</v>
+        <v>82634</v>
       </c>
       <c r="F51" t="n">
-        <v>1052124.507172404</v>
+        <v>1036432.557235319</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>18-02</t>
+          <t>18-09</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>43132</v>
+        <v>43344</v>
       </c>
       <c r="D52" t="n">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="E52" t="n">
-        <v>91242.5</v>
+        <v>108680</v>
       </c>
       <c r="F52" t="n">
-        <v>1052829.922652547</v>
+        <v>1034530.606536008</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>18-07</t>
+          <t>18-10</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>43282</v>
+        <v>43374</v>
       </c>
       <c r="D53" t="n">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="E53" t="n">
-        <v>119044.5</v>
+        <v>130830</v>
       </c>
       <c r="F53" t="n">
-        <v>1031020.024357838</v>
+        <v>1029548.171895577</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>18-08</t>
+          <t>18-11</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>43313</v>
+        <v>43405</v>
       </c>
       <c r="D54" t="n">
-        <v>79</v>
+        <v>127</v>
       </c>
       <c r="E54" t="n">
-        <v>82634</v>
+        <v>134643.5</v>
       </c>
       <c r="F54" t="n">
-        <v>1036432.557235319</v>
+        <v>1034085.201898285</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>18-09</t>
+          <t>18-12</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>43344</v>
+        <v>43435</v>
       </c>
       <c r="D55" t="n">
-        <v>105</v>
+        <v>11</v>
       </c>
       <c r="E55" t="n">
-        <v>108680</v>
+        <v>11206</v>
       </c>
       <c r="F55" t="n">
-        <v>1034530.606536008</v>
+        <v>1060542.54068505</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>18-10</t>
+          <t>18-12</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>43374</v>
+        <v>43435</v>
       </c>
       <c r="D56" t="n">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="E56" t="n">
-        <v>130830</v>
+        <v>116757</v>
       </c>
       <c r="F56" t="n">
-        <v>1029548.171895577</v>
+        <v>1031716.384874854</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>18-11</t>
+          <t>19-01</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>43405</v>
+        <v>43466</v>
       </c>
       <c r="D57" t="n">
-        <v>127</v>
+        <v>5</v>
       </c>
       <c r="E57" t="n">
-        <v>134643.5</v>
+        <v>5428.833333333333</v>
       </c>
       <c r="F57" t="n">
-        <v>1034085.201898285</v>
+        <v>1015606.072514045</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
+        <v>37</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>19-01</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>43466</v>
+      </c>
+      <c r="D58" t="n">
         <v>40</v>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>18-12</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="n">
-        <v>43435</v>
-      </c>
-      <c r="D58" t="n">
-        <v>11</v>
-      </c>
       <c r="E58" t="n">
-        <v>11206</v>
+        <v>42104</v>
       </c>
       <c r="F58" t="n">
-        <v>1060542.54068505</v>
+        <v>1016234.04199126</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>18-12</t>
+          <t>19-02</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>43435</v>
+        <v>43497</v>
       </c>
       <c r="D59" t="n">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="E59" t="n">
-        <v>116757</v>
+        <v>137453.6190476191</v>
       </c>
       <c r="F59" t="n">
-        <v>1031716.384874854</v>
+        <v>1026978.377371882</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>19-01</t>
+          <t>19-03</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
-        <v>43466</v>
+        <v>43525</v>
       </c>
       <c r="D60" t="n">
-        <v>5</v>
+        <v>136</v>
       </c>
       <c r="E60" t="n">
-        <v>5428.833333333333</v>
+        <v>145003</v>
       </c>
       <c r="F60" t="n">
-        <v>1015606.072514045</v>
+        <v>1032358.532666807</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>19-01</t>
+          <t>19-04</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>43466</v>
+        <v>43556</v>
       </c>
       <c r="D61" t="n">
-        <v>40</v>
+        <v>149</v>
       </c>
       <c r="E61" t="n">
-        <v>42104</v>
+        <v>157371.5</v>
       </c>
       <c r="F61" t="n">
-        <v>1016234.04199126</v>
+        <v>1025429.09470863</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>19-02</t>
+          <t>19-05</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>43497</v>
+        <v>43586</v>
       </c>
       <c r="D62" t="n">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="E62" t="n">
-        <v>137453.6190476191</v>
+        <v>120735.5</v>
       </c>
       <c r="F62" t="n">
-        <v>1026978.377371882</v>
+        <v>1058188.788934227</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>19-03</t>
+          <t>19-06</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
-        <v>43525</v>
+        <v>43617</v>
       </c>
       <c r="D63" t="n">
-        <v>136</v>
+        <v>1</v>
       </c>
       <c r="E63" t="n">
-        <v>145003</v>
+        <v>986</v>
       </c>
       <c r="F63" t="n">
-        <v>1032358.532666807</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>19-04</t>
+          <t>19-06</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
-        <v>43556</v>
+        <v>43617</v>
       </c>
       <c r="D64" t="n">
-        <v>149</v>
+        <v>56</v>
       </c>
       <c r="E64" t="n">
-        <v>157371.5</v>
+        <v>58460.5</v>
       </c>
       <c r="F64" t="n">
-        <v>1025429.09470863</v>
+        <v>1011609.460490417</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>19-05</t>
+          <t>19-07</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
-        <v>43586</v>
+        <v>43647</v>
       </c>
       <c r="D65" t="n">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="E65" t="n">
-        <v>120735.5</v>
+        <v>111372</v>
       </c>
       <c r="F65" t="n">
-        <v>1058188.788934227</v>
+        <v>1034999.517965497</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>19-06</t>
+          <t>19-08</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
-        <v>43617</v>
+        <v>43678</v>
       </c>
       <c r="D66" t="n">
-        <v>1</v>
+        <v>153</v>
       </c>
       <c r="E66" t="n">
-        <v>986</v>
+        <v>160096</v>
       </c>
       <c r="F66" t="n">
-        <v>1000000</v>
+        <v>1034548.846668561</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>19-06</t>
+          <t>19-09</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
-        <v>43617</v>
+        <v>43709</v>
       </c>
       <c r="D67" t="n">
-        <v>56</v>
+        <v>123</v>
       </c>
       <c r="E67" t="n">
-        <v>58460.5</v>
+        <v>127447.5</v>
       </c>
       <c r="F67" t="n">
-        <v>1011609.460490417</v>
+        <v>1031781.204367694</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>19-07</t>
+          <t>19-10</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
-        <v>43647</v>
+        <v>43739</v>
       </c>
       <c r="D68" t="n">
-        <v>107</v>
+        <v>54</v>
       </c>
       <c r="E68" t="n">
-        <v>111372</v>
+        <v>57919</v>
       </c>
       <c r="F68" t="n">
-        <v>1034999.517965497</v>
+        <v>1035277.435479837</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>19-08</t>
+          <t>19-11</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
-        <v>43678</v>
+        <v>43770</v>
       </c>
       <c r="D69" t="n">
-        <v>145</v>
+        <v>13</v>
       </c>
       <c r="E69" t="n">
-        <v>151479</v>
+        <v>14036</v>
       </c>
       <c r="F69" t="n">
-        <v>1033920.925170045</v>
+        <v>1182940.118285124</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>19-08</t>
+          <t>19-11</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
-        <v>43678</v>
+        <v>43770</v>
       </c>
       <c r="D70" t="n">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E70" t="n">
-        <v>8617</v>
+        <v>75240</v>
       </c>
       <c r="F70" t="n">
-        <v>1045587.133853623</v>
+        <v>1034228.662443027</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>19-09</t>
+          <t>19-12</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>43709</v>
+        <v>43800</v>
       </c>
       <c r="D71" t="n">
-        <v>123</v>
+        <v>16</v>
       </c>
       <c r="E71" t="n">
-        <v>127447.5</v>
+        <v>16632.33333333333</v>
       </c>
       <c r="F71" t="n">
-        <v>1031781.204367694</v>
+        <v>1017278.53118925</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>19-10</t>
+          <t>19-12</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
-        <v>43739</v>
+        <v>43800</v>
       </c>
       <c r="D72" t="n">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="E72" t="n">
-        <v>57919</v>
+        <v>18818</v>
       </c>
       <c r="F72" t="n">
-        <v>1035277.435479837</v>
+        <v>1041100.257979948</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>19-11</t>
+          <t>20-01</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>43770</v>
+        <v>43831</v>
       </c>
       <c r="D73" t="n">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="E73" t="n">
-        <v>14036</v>
+        <v>60002.25</v>
       </c>
       <c r="F73" t="n">
-        <v>1182940.118285124</v>
+        <v>1056519.747065735</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>19-11</t>
+          <t>20-01</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
-        <v>43770</v>
+        <v>43831</v>
       </c>
       <c r="D74" t="n">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="E74" t="n">
-        <v>75240</v>
+        <v>38388</v>
       </c>
       <c r="F74" t="n">
-        <v>1034228.662443027</v>
+        <v>1058439.367117763</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>19-12</t>
+          <t>20-02</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>43800</v>
+        <v>43862</v>
       </c>
       <c r="D75" t="n">
-        <v>16</v>
+        <v>98</v>
       </c>
       <c r="E75" t="n">
-        <v>16632.33333333333</v>
+        <v>106582</v>
       </c>
       <c r="F75" t="n">
-        <v>1017278.53118925</v>
+        <v>1024017.583328642</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>19-12</t>
+          <t>20-03</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
-        <v>43800</v>
+        <v>43891</v>
       </c>
       <c r="D76" t="n">
-        <v>18</v>
+        <v>157</v>
       </c>
       <c r="E76" t="n">
-        <v>18818</v>
+        <v>171826</v>
       </c>
       <c r="F76" t="n">
-        <v>1041100.257979948</v>
+        <v>1032925.39734219</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>20-01</t>
+          <t>20-04</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
-        <v>43831</v>
+        <v>43922</v>
       </c>
       <c r="D77" t="n">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="E77" t="n">
-        <v>60002.25</v>
+        <v>29493.5</v>
       </c>
       <c r="F77" t="n">
-        <v>1056519.747065735</v>
+        <v>1035227.493765236</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>20-01</t>
+          <t>20-04</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>43831</v>
+        <v>43922</v>
       </c>
       <c r="D78" t="n">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="E78" t="n">
-        <v>38388</v>
+        <v>73404</v>
       </c>
       <c r="F78" t="n">
-        <v>1058439.367117763</v>
+        <v>1050668.148864503</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>20-02</t>
+          <t>20-05</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
-        <v>43862</v>
+        <v>43952</v>
       </c>
       <c r="D79" t="n">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="E79" t="n">
-        <v>106582</v>
+        <v>82789</v>
       </c>
       <c r="F79" t="n">
-        <v>1024017.583328642</v>
+        <v>1032110.859008302</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>20-03</t>
+          <t>20-05</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
-        <v>43891</v>
+        <v>43952</v>
       </c>
       <c r="D80" t="n">
-        <v>157</v>
+        <v>46</v>
       </c>
       <c r="E80" t="n">
-        <v>171826</v>
+        <v>51229.5</v>
       </c>
       <c r="F80" t="n">
-        <v>1032925.39734219</v>
+        <v>1038494.719829525</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>20-04</t>
+          <t>20-06</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
-        <v>43922</v>
+        <v>43983</v>
       </c>
       <c r="D81" t="n">
-        <v>27</v>
+        <v>132</v>
       </c>
       <c r="E81" t="n">
-        <v>29493.5</v>
+        <v>143498.5</v>
       </c>
       <c r="F81" t="n">
-        <v>1035227.493765236</v>
+        <v>1035253.791768584</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>20-04</t>
+          <t>20-07</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>43922</v>
+        <v>44013</v>
       </c>
       <c r="D82" t="n">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="E82" t="n">
-        <v>73404</v>
+        <v>95465</v>
       </c>
       <c r="F82" t="n">
-        <v>1050668.148864503</v>
+        <v>1029825.069411695</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>20-05</t>
+          <t>20-08</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>43952</v>
+        <v>44044</v>
       </c>
       <c r="D83" t="n">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="E83" t="n">
-        <v>82789</v>
+        <v>6397</v>
       </c>
       <c r="F83" t="n">
-        <v>1032110.859008302</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>20-05</t>
+          <t>20-08</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
-        <v>43952</v>
+        <v>44044</v>
       </c>
       <c r="D84" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="E84" t="n">
-        <v>51229.5</v>
+        <v>30053</v>
       </c>
       <c r="F84" t="n">
-        <v>1038494.719829525</v>
+        <v>1023487.336066505</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>20-06</t>
+          <t>20-09</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
-        <v>43983</v>
+        <v>44075</v>
       </c>
       <c r="D85" t="n">
-        <v>132</v>
+        <v>93</v>
       </c>
       <c r="E85" t="n">
-        <v>143498.5</v>
+        <v>99433</v>
       </c>
       <c r="F85" t="n">
-        <v>1035253.791768584</v>
+        <v>1024182.43961676</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>20-07</t>
+          <t>20-10</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
-        <v>44013</v>
+        <v>44105</v>
       </c>
       <c r="D86" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E86" t="n">
-        <v>95465</v>
+        <v>99007.5</v>
       </c>
       <c r="F86" t="n">
-        <v>1029825.069411695</v>
+        <v>1019625.996821655</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>20-08</t>
+          <t>20-11</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
-        <v>44044</v>
+        <v>44136</v>
       </c>
       <c r="D87" t="n">
-        <v>6</v>
+        <v>91</v>
       </c>
       <c r="E87" t="n">
-        <v>6397</v>
+        <v>97187</v>
       </c>
       <c r="F87" t="n">
-        <v>1000000</v>
+        <v>1037740.892561077</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>20-08</t>
+          <t>20-12</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
-        <v>44044</v>
+        <v>44166</v>
       </c>
       <c r="D88" t="n">
-        <v>28</v>
+        <v>155</v>
       </c>
       <c r="E88" t="n">
-        <v>30053</v>
+        <v>172196.75</v>
       </c>
       <c r="F88" t="n">
-        <v>1023487.336066505</v>
+        <v>1034500.349565062</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>20-09</t>
+          <t>21-01</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
-        <v>44075</v>
+        <v>44197</v>
       </c>
       <c r="D89" t="n">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="E89" t="n">
-        <v>99433</v>
+        <v>118846</v>
       </c>
       <c r="F89" t="n">
-        <v>1024182.43961676</v>
+        <v>1038450.004159809</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>20-10</t>
+          <t>21-02</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
-        <v>44105</v>
+        <v>44228</v>
       </c>
       <c r="D90" t="n">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="E90" t="n">
-        <v>99007.5</v>
+        <v>90689</v>
       </c>
       <c r="F90" t="n">
-        <v>1019625.996821655</v>
+        <v>1023782.559911382</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>20-11</t>
+          <t>21-03</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
-        <v>44136</v>
+        <v>44256</v>
       </c>
       <c r="D91" t="n">
-        <v>91</v>
+        <v>178</v>
       </c>
       <c r="E91" t="n">
-        <v>97187</v>
+        <v>195600</v>
       </c>
       <c r="F91" t="n">
-        <v>1037740.892561077</v>
+        <v>1028023.229392489</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>20-12</t>
+          <t>21-04</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
-        <v>44166</v>
+        <v>44287</v>
       </c>
       <c r="D92" t="n">
-        <v>155</v>
+        <v>109</v>
       </c>
       <c r="E92" t="n">
-        <v>172196.75</v>
+        <v>118685.5</v>
       </c>
       <c r="F92" t="n">
-        <v>1034500.349565062</v>
+        <v>1028696.824598203</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>21-01</t>
+          <t>21-05</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
-        <v>44197</v>
+        <v>44317</v>
       </c>
       <c r="D93" t="n">
-        <v>111</v>
+        <v>41</v>
       </c>
       <c r="E93" t="n">
-        <v>118846</v>
+        <v>44043.5</v>
       </c>
       <c r="F93" t="n">
-        <v>1038450.004159809</v>
+        <v>1053605.26366244</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>21-02</t>
+          <t>21-06</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
-        <v>44228</v>
+        <v>44348</v>
       </c>
       <c r="D94" t="n">
-        <v>83</v>
+        <v>170</v>
       </c>
       <c r="E94" t="n">
-        <v>90689</v>
+        <v>188104.5</v>
       </c>
       <c r="F94" t="n">
-        <v>1023782.559911382</v>
+        <v>1037585.633581059</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>21-03</t>
+          <t>21-07</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
-        <v>44256</v>
+        <v>44378</v>
       </c>
       <c r="D95" t="n">
-        <v>178</v>
+        <v>151</v>
       </c>
       <c r="E95" t="n">
-        <v>195600</v>
+        <v>170701.5</v>
       </c>
       <c r="F95" t="n">
-        <v>1028023.229392489</v>
+        <v>1030588.30862034</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>21-04</t>
+          <t>21-08</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
-        <v>44287</v>
+        <v>44409</v>
       </c>
       <c r="D96" t="n">
-        <v>109</v>
+        <v>9</v>
       </c>
       <c r="E96" t="n">
-        <v>118685.5</v>
+        <v>9906</v>
       </c>
       <c r="F96" t="n">
-        <v>1028696.824598203</v>
+        <v>1041521.386408238</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>21-05</t>
+          <t>21-08</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
-        <v>44317</v>
+        <v>44409</v>
       </c>
       <c r="D97" t="n">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="E97" t="n">
-        <v>44043.5</v>
+        <v>66908</v>
       </c>
       <c r="F97" t="n">
-        <v>1053605.26366244</v>
+        <v>1024553.635168067</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>21-06</t>
+          <t>21-09</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
-        <v>44348</v>
+        <v>44440</v>
       </c>
       <c r="D98" t="n">
-        <v>170</v>
+        <v>72</v>
       </c>
       <c r="E98" t="n">
-        <v>188104.5</v>
+        <v>81175</v>
       </c>
       <c r="F98" t="n">
-        <v>1037585.633581059</v>
+        <v>1030326.852190565</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>21-07</t>
+          <t>21-10</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
-        <v>44378</v>
+        <v>44470</v>
       </c>
       <c r="D99" t="n">
-        <v>151</v>
+        <v>42</v>
       </c>
       <c r="E99" t="n">
-        <v>170701.5</v>
+        <v>47602</v>
       </c>
       <c r="F99" t="n">
-        <v>1030588.30862034</v>
+        <v>1036296.715060887</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>21-08</t>
+          <t>21-11</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
-        <v>44409</v>
+        <v>44501</v>
       </c>
       <c r="D100" t="n">
-        <v>9</v>
+        <v>80</v>
       </c>
       <c r="E100" t="n">
-        <v>9906</v>
+        <v>90071</v>
       </c>
       <c r="F100" t="n">
-        <v>1041521.386408238</v>
+        <v>1036290.342814372</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>21-08</t>
+          <t>21-12</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
-        <v>44409</v>
+        <v>44531</v>
       </c>
       <c r="D101" t="n">
-        <v>59</v>
+        <v>121</v>
       </c>
       <c r="E101" t="n">
-        <v>66908</v>
+        <v>134403</v>
       </c>
       <c r="F101" t="n">
-        <v>1024553.635168067</v>
+        <v>1034602.481633433</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>21-09</t>
+          <t>22-01</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
-        <v>44440</v>
+        <v>44562</v>
       </c>
       <c r="D102" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="E102" t="n">
-        <v>81175</v>
+        <v>73406.83333333333</v>
       </c>
       <c r="F102" t="n">
-        <v>1030326.852190565</v>
+        <v>1044746.086115999</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>21-10</t>
+          <t>22-02</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
-        <v>44470</v>
+        <v>44593</v>
       </c>
       <c r="D103" t="n">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="E103" t="n">
-        <v>17562</v>
+        <v>43824.5</v>
       </c>
       <c r="F103" t="n">
-        <v>1005841.475568557</v>
+        <v>1018035.742546445</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>21-10</t>
+          <t>22-02</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
-        <v>44470</v>
+        <v>44593</v>
       </c>
       <c r="D104" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="E104" t="n">
-        <v>30040</v>
+        <v>53718</v>
       </c>
       <c r="F104" t="n">
-        <v>1054101.472583001</v>
+        <v>1037287.47926955</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>21-11</t>
+          <t>22-03</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
-        <v>44501</v>
+        <v>44621</v>
       </c>
       <c r="D105" t="n">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="E105" t="n">
-        <v>90071</v>
+        <v>58130</v>
       </c>
       <c r="F105" t="n">
-        <v>1036290.342814372</v>
+        <v>1030982.195847511</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>21-12</t>
+          <t>22-03</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
-        <v>44531</v>
+        <v>44621</v>
       </c>
       <c r="D106" t="n">
-        <v>121</v>
+        <v>56</v>
       </c>
       <c r="E106" t="n">
-        <v>134403</v>
+        <v>63001</v>
       </c>
       <c r="F106" t="n">
-        <v>1034602.481633433</v>
+        <v>1033340.799110742</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>22-01</t>
+          <t>22-04</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
-        <v>44562</v>
+        <v>44652</v>
       </c>
       <c r="D107" t="n">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="E107" t="n">
-        <v>73406.83333333333</v>
+        <v>55322.5</v>
       </c>
       <c r="F107" t="n">
-        <v>1044746.086115999</v>
+        <v>1035889.531981563</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>22-02</t>
+          <t>22-04</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
-        <v>44593</v>
+        <v>44652</v>
       </c>
       <c r="D108" t="n">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="E108" t="n">
-        <v>43824.5</v>
+        <v>15643</v>
       </c>
       <c r="F108" t="n">
-        <v>1018035.742546445</v>
+        <v>1034090.996702465</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>22-02</t>
+          <t>22-05</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
-        <v>44593</v>
+        <v>44682</v>
       </c>
       <c r="D109" t="n">
-        <v>48</v>
+        <v>172</v>
       </c>
       <c r="E109" t="n">
-        <v>53718</v>
+        <v>190465.5</v>
       </c>
       <c r="F109" t="n">
-        <v>1037287.47926955</v>
+        <v>1028557.019862775</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>22-03</t>
+          <t>22-06</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
-        <v>44621</v>
+        <v>44713</v>
       </c>
       <c r="D110" t="n">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="E110" t="n">
-        <v>58130</v>
+        <v>27689</v>
       </c>
       <c r="F110" t="n">
-        <v>1030982.195847511</v>
+        <v>1046170.864564147</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>22-03</t>
+          <t>22-06</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
-        <v>44621</v>
+        <v>44713</v>
       </c>
       <c r="D111" t="n">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="E111" t="n">
-        <v>63001</v>
+        <v>88652.29761904762</v>
       </c>
       <c r="F111" t="n">
-        <v>1033340.799110742</v>
+        <v>1034150.449811112</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>22-04</t>
+          <t>22-07</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
-        <v>44652</v>
+        <v>44743</v>
       </c>
       <c r="D112" t="n">
-        <v>49</v>
+        <v>107</v>
       </c>
       <c r="E112" t="n">
-        <v>55322.5</v>
+        <v>117563</v>
       </c>
       <c r="F112" t="n">
-        <v>1035889.531981563</v>
+        <v>1033684.1307364</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>22-04</t>
+          <t>22-08</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
-        <v>44652</v>
+        <v>44774</v>
       </c>
       <c r="D113" t="n">
-        <v>14</v>
+        <v>83</v>
       </c>
       <c r="E113" t="n">
-        <v>15643</v>
+        <v>90290.5</v>
       </c>
       <c r="F113" t="n">
-        <v>1034090.996702465</v>
+        <v>1025233.167816732</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>22-05</t>
+          <t>22-09</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
-        <v>44682</v>
+        <v>44805</v>
       </c>
       <c r="D114" t="n">
-        <v>172</v>
+        <v>10</v>
       </c>
       <c r="E114" t="n">
-        <v>190465.5</v>
+        <v>10767</v>
       </c>
       <c r="F114" t="n">
-        <v>1028557.019862775</v>
+        <v>1003239.318333798</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>22-06</t>
+          <t>22-09</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
-        <v>44713</v>
+        <v>44805</v>
       </c>
       <c r="D115" t="n">
-        <v>25</v>
+        <v>88</v>
       </c>
       <c r="E115" t="n">
-        <v>27689</v>
+        <v>97453.5</v>
       </c>
       <c r="F115" t="n">
-        <v>1046170.864564147</v>
+        <v>1036443.428674051</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>22-06</t>
+          <t>22-10</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
-        <v>44713</v>
+        <v>44835</v>
       </c>
       <c r="D116" t="n">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="E116" t="n">
-        <v>88652.29761904762</v>
+        <v>41506</v>
       </c>
       <c r="F116" t="n">
-        <v>1034150.449811112</v>
+        <v>1032005.187275635</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>22-07</t>
+          <t>22-11</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
-        <v>44743</v>
+        <v>44866</v>
       </c>
       <c r="D117" t="n">
-        <v>29</v>
+        <v>174</v>
       </c>
       <c r="E117" t="n">
-        <v>31652</v>
+        <v>181951.5</v>
       </c>
       <c r="F117" t="n">
-        <v>1029241.68141297</v>
+        <v>1033648.929845238</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>22-07</t>
+          <t>22-12</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
-        <v>44743</v>
+        <v>44896</v>
       </c>
       <c r="D118" t="n">
-        <v>78</v>
+        <v>10</v>
       </c>
       <c r="E118" t="n">
-        <v>85911</v>
+        <v>9925</v>
       </c>
       <c r="F118" t="n">
-        <v>1035320.852529711</v>
+        <v>1014242.138916877</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>22-08</t>
+          <t>23-01</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
-        <v>44774</v>
+        <v>44927</v>
       </c>
       <c r="D119" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="E119" t="n">
-        <v>90290.5</v>
+        <v>90428</v>
       </c>
       <c r="F119" t="n">
-        <v>1025233.167816732</v>
+        <v>1035001.575142849</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>22-09</t>
+          <t>23-02</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
-        <v>44805</v>
+        <v>44958</v>
       </c>
       <c r="D120" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="E120" t="n">
-        <v>10767</v>
+        <v>45805</v>
       </c>
       <c r="F120" t="n">
-        <v>1003239.318333798</v>
+        <v>1032511.082395335</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>22-09</t>
+          <t>23-03</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
-        <v>44805</v>
+        <v>44986</v>
       </c>
       <c r="D121" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E121" t="n">
-        <v>97453.5</v>
+        <v>95825.5</v>
       </c>
       <c r="F121" t="n">
-        <v>1036443.428674051</v>
+        <v>1029443.431120622</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>22-10</t>
+          <t>23-04</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
-        <v>44835</v>
+        <v>45017</v>
       </c>
       <c r="D122" t="n">
-        <v>38</v>
+        <v>114</v>
       </c>
       <c r="E122" t="n">
-        <v>41506</v>
+        <v>120704.5</v>
       </c>
       <c r="F122" t="n">
-        <v>1032005.187275635</v>
+        <v>1033348.78627235</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>22-11</t>
+          <t>23-05</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
-        <v>44866</v>
+        <v>45047</v>
       </c>
       <c r="D123" t="n">
-        <v>174</v>
+        <v>85</v>
       </c>
       <c r="E123" t="n">
-        <v>181951.5</v>
+        <v>90900</v>
       </c>
       <c r="F123" t="n">
-        <v>1033648.929845238</v>
+        <v>1030717.911847396</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>22-12</t>
+          <t>23-06</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
-        <v>44896</v>
+        <v>45078</v>
       </c>
       <c r="D124" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="E124" t="n">
-        <v>9925</v>
+        <v>75512</v>
       </c>
       <c r="F124" t="n">
-        <v>1014242.138916877</v>
+        <v>1031776.831942892</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>23-01</t>
+          <t>23-07</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
-        <v>44927</v>
+        <v>45108</v>
       </c>
       <c r="D125" t="n">
-        <v>89</v>
+        <v>119</v>
       </c>
       <c r="E125" t="n">
-        <v>90428</v>
+        <v>122405</v>
       </c>
       <c r="F125" t="n">
-        <v>1035001.575142849</v>
+        <v>1039059.527920769</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>23-02</t>
+          <t>23-08</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
-        <v>44958</v>
+        <v>45139</v>
       </c>
       <c r="D126" t="n">
-        <v>44</v>
+        <v>126</v>
       </c>
       <c r="E126" t="n">
-        <v>45805</v>
+        <v>130916</v>
       </c>
       <c r="F126" t="n">
-        <v>1032511.082395335</v>
+        <v>1029366.64215143</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>23-03</t>
+          <t>23-09</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
-        <v>44986</v>
+        <v>45170</v>
       </c>
       <c r="D127" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E127" t="n">
-        <v>95825.5</v>
+        <v>92814</v>
       </c>
       <c r="F127" t="n">
-        <v>1029443.431120622</v>
+        <v>1022414.564199268</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>23-04</t>
+          <t>23-10</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
-        <v>45017</v>
+        <v>45200</v>
       </c>
       <c r="D128" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E128" t="n">
-        <v>120704.5</v>
+        <v>122602</v>
       </c>
       <c r="F128" t="n">
-        <v>1033348.78627235</v>
+        <v>1038463.76475326</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>23-05</t>
+          <t>24-01</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
-        <v>45047</v>
+        <v>45292</v>
       </c>
       <c r="D129" t="n">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="E129" t="n">
-        <v>90900</v>
+        <v>111998</v>
       </c>
       <c r="F129" t="n">
-        <v>1030717.911847396</v>
+        <v>1033812.463383833</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>23-06</t>
+          <t>24-02</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
-        <v>45078</v>
+        <v>45323</v>
       </c>
       <c r="D130" t="n">
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="E130" t="n">
-        <v>75512</v>
+        <v>116814.5</v>
       </c>
       <c r="F130" t="n">
-        <v>1031776.831942892</v>
+        <v>1018570.819449762</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>23-07</t>
+          <t>24-03</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
-        <v>45108</v>
+        <v>45352</v>
       </c>
       <c r="D131" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="E131" t="n">
-        <v>77956.5</v>
+        <v>85814.5</v>
       </c>
       <c r="F131" t="n">
-        <v>1037499.856228495</v>
+        <v>1022979.65544836</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>23-07</t>
+          <t>24-05</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
-        <v>45108</v>
+        <v>45413</v>
       </c>
       <c r="D132" t="n">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="E132" t="n">
-        <v>44448.5</v>
+        <v>5644</v>
       </c>
       <c r="F132" t="n">
-        <v>1041794.975602439</v>
+        <v>1024043.225076778</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>23-08</t>
+          <t>24-06</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
-        <v>45139</v>
+        <v>45444</v>
       </c>
       <c r="D133" t="n">
-        <v>126</v>
+        <v>16</v>
       </c>
       <c r="E133" t="n">
-        <v>130916</v>
+        <v>16288</v>
       </c>
       <c r="F133" t="n">
-        <v>1029366.64215143</v>
+        <v>1037731.522946341</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>23-09</t>
+          <t>24-06</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
-        <v>45170</v>
+        <v>45444</v>
       </c>
       <c r="D134" t="n">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="E134" t="n">
-        <v>90862</v>
+        <v>73207</v>
       </c>
       <c r="F134" t="n">
-        <v>1022896.099156862</v>
+        <v>1047566.345766878</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>23-09</t>
+          <t>24-07</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
-        <v>45170</v>
+        <v>45474</v>
       </c>
       <c r="D135" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="E135" t="n">
-        <v>1952</v>
+        <v>23744</v>
       </c>
       <c r="F135" t="n">
-        <v>1000000</v>
+        <v>1024593.591005447</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>23-10</t>
+          <t>24-07</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
-        <v>45200</v>
+        <v>45474</v>
       </c>
       <c r="D136" t="n">
-        <v>116</v>
+        <v>43</v>
       </c>
       <c r="E136" t="n">
-        <v>122602</v>
+        <v>43185</v>
       </c>
       <c r="F136" t="n">
-        <v>1038463.76475326</v>
+        <v>1026886.302670507</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>24-01</t>
+          <t>24-08</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
-        <v>45292</v>
+        <v>45505</v>
       </c>
       <c r="D137" t="n">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="E137" t="n">
-        <v>32629</v>
+        <v>59209.5</v>
       </c>
       <c r="F137" t="n">
-        <v>1038892.106698872</v>
+        <v>1027721.702525777</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>24-01</t>
+          <t>24-08</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
-        <v>45292</v>
+        <v>45505</v>
       </c>
       <c r="D138" t="n">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="E138" t="n">
-        <v>79369</v>
+        <v>25079</v>
       </c>
       <c r="F138" t="n">
-        <v>1031724.196154481</v>
+        <v>1031458.702218323</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>24-02</t>
+          <t>24-09</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
-        <v>45323</v>
+        <v>45536</v>
       </c>
       <c r="D139" t="n">
-        <v>108</v>
+        <v>160</v>
       </c>
       <c r="E139" t="n">
-        <v>116814.5</v>
+        <v>168860.5</v>
       </c>
       <c r="F139" t="n">
-        <v>1018570.819449762</v>
+        <v>1019205.539277288</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>24-03</t>
+          <t>24-10</t>
         </is>
       </c>
       <c r="C140" s="2" t="n">
-        <v>45352</v>
+        <v>45566</v>
       </c>
       <c r="D140" t="n">
-        <v>81</v>
+        <v>125</v>
       </c>
       <c r="E140" t="n">
-        <v>85814.5</v>
+        <v>132212</v>
       </c>
       <c r="F140" t="n">
-        <v>1022979.65544836</v>
+        <v>1033747.129775336</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>24-05</t>
+          <t>24-11</t>
         </is>
       </c>
       <c r="C141" s="2" t="n">
-        <v>45413</v>
+        <v>45597</v>
       </c>
       <c r="D141" t="n">
-        <v>5</v>
+        <v>84</v>
       </c>
       <c r="E141" t="n">
-        <v>5644</v>
+        <v>91917</v>
       </c>
       <c r="F141" t="n">
-        <v>1024043.225076778</v>
+        <v>1039538.137430717</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>24-06</t>
+          <t>24-12</t>
         </is>
       </c>
       <c r="C142" s="2" t="n">
-        <v>45444</v>
+        <v>45627</v>
       </c>
       <c r="D142" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E142" t="n">
-        <v>16288</v>
+        <v>22835.5</v>
       </c>
       <c r="F142" t="n">
-        <v>1037731.522946341</v>
+        <v>1012791.855792881</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>24-06</t>
+          <t>24-12</t>
         </is>
       </c>
       <c r="C143" s="2" t="n">
-        <v>45444</v>
+        <v>45627</v>
       </c>
       <c r="D143" t="n">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="E143" t="n">
-        <v>73207</v>
+        <v>46780</v>
       </c>
       <c r="F143" t="n">
-        <v>1047566.345766878</v>
+        <v>1032032.01281388</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>24-07</t>
+          <t>25-01</t>
         </is>
       </c>
       <c r="C144" s="2" t="n">
-        <v>45474</v>
+        <v>45658</v>
       </c>
       <c r="D144" t="n">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="E144" t="n">
-        <v>23744</v>
+        <v>54882.66666666666</v>
       </c>
       <c r="F144" t="n">
-        <v>1024593.591005447</v>
+        <v>1035103.349864549</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>24-07</t>
+          <t>25-01</t>
         </is>
       </c>
       <c r="C145" s="2" t="n">
-        <v>45474</v>
+        <v>45658</v>
       </c>
       <c r="D145" t="n">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="E145" t="n">
-        <v>43185</v>
+        <v>70826</v>
       </c>
       <c r="F145" t="n">
-        <v>1026886.302670507</v>
+        <v>1018786.433383197</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>24-08</t>
+          <t>25-02</t>
         </is>
       </c>
       <c r="C146" s="2" t="n">
-        <v>45505</v>
+        <v>45689</v>
       </c>
       <c r="D146" t="n">
-        <v>59</v>
+        <v>108</v>
       </c>
       <c r="E146" t="n">
-        <v>59209.5</v>
+        <v>115525</v>
       </c>
       <c r="F146" t="n">
-        <v>1027721.702525777</v>
+        <v>1027263.255447782</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>24-08</t>
+          <t>25-03</t>
         </is>
       </c>
       <c r="C147" s="2" t="n">
-        <v>45505</v>
+        <v>45717</v>
       </c>
       <c r="D147" t="n">
-        <v>25</v>
+        <v>129</v>
       </c>
       <c r="E147" t="n">
-        <v>25079</v>
+        <v>137849</v>
       </c>
       <c r="F147" t="n">
-        <v>1031458.702218323</v>
+        <v>1023912.707064348</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>24-09</t>
+          <t>25-04</t>
         </is>
       </c>
       <c r="C148" s="2" t="n">
-        <v>45536</v>
+        <v>45748</v>
       </c>
       <c r="D148" t="n">
-        <v>160</v>
+        <v>48</v>
       </c>
       <c r="E148" t="n">
-        <v>168860.5</v>
+        <v>52549</v>
       </c>
       <c r="F148" t="n">
-        <v>1019205.539277288</v>
+        <v>1007127.512720508</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>24-10</t>
+          <t>25-05</t>
         </is>
       </c>
       <c r="C149" s="2" t="n">
-        <v>45566</v>
+        <v>45778</v>
       </c>
       <c r="D149" t="n">
-        <v>125</v>
+        <v>27</v>
       </c>
       <c r="E149" t="n">
-        <v>132212</v>
+        <v>27279.16666666667</v>
       </c>
       <c r="F149" t="n">
-        <v>1033747.129775336</v>
+        <v>1054682.526338781</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>24-11</t>
+          <t>25-05</t>
         </is>
       </c>
       <c r="C150" s="2" t="n">
-        <v>45597</v>
+        <v>45778</v>
       </c>
       <c r="D150" t="n">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="E150" t="n">
-        <v>91917</v>
+        <v>20657.66666666667</v>
       </c>
       <c r="F150" t="n">
-        <v>1039538.137430717</v>
+        <v>990012.6335985024</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>24-12</t>
+          <t>25-06</t>
         </is>
       </c>
       <c r="C151" s="2" t="n">
-        <v>45627</v>
+        <v>45809</v>
       </c>
       <c r="D151" t="n">
-        <v>21</v>
+        <v>123</v>
       </c>
       <c r="E151" t="n">
-        <v>22835.5</v>
+        <v>134440.2</v>
       </c>
       <c r="F151" t="n">
-        <v>1012791.855792881</v>
+        <v>1024928.951634053</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>24-12</t>
+          <t>25-07</t>
         </is>
       </c>
       <c r="C152" s="2" t="n">
-        <v>45627</v>
+        <v>45839</v>
       </c>
       <c r="D152" t="n">
-        <v>43</v>
+        <v>133</v>
       </c>
       <c r="E152" t="n">
-        <v>46780</v>
+        <v>141092.5</v>
       </c>
       <c r="F152" t="n">
-        <v>1032032.01281388</v>
+        <v>1043780.604139672</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>25-01</t>
+          <t>25-08</t>
         </is>
       </c>
       <c r="C153" s="2" t="n">
-        <v>45658</v>
+        <v>45870</v>
       </c>
       <c r="D153" t="n">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="E153" t="n">
-        <v>54882.66666666666</v>
+        <v>66573</v>
       </c>
       <c r="F153" t="n">
-        <v>1035103.349864549</v>
+        <v>1022804.723592447</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>25-01</t>
+          <t>25-09</t>
         </is>
       </c>
       <c r="C154" s="2" t="n">
-        <v>45658</v>
+        <v>45901</v>
       </c>
       <c r="D154" t="n">
-        <v>66</v>
+        <v>146</v>
       </c>
       <c r="E154" t="n">
-        <v>70826</v>
+        <v>155394</v>
       </c>
       <c r="F154" t="n">
-        <v>1018786.433383197</v>
+        <v>1022796.452305108</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>25-02</t>
+          <t>25-11</t>
         </is>
       </c>
       <c r="C155" s="2" t="n">
-        <v>45689</v>
+        <v>45962</v>
       </c>
       <c r="D155" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E155" t="n">
-        <v>73599.5</v>
+        <v>75319</v>
       </c>
       <c r="F155" t="n">
-        <v>1024652.517726434</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="n">
-        <v>101</v>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>25-02</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="n">
-        <v>45689</v>
-      </c>
-      <c r="D156" t="n">
-        <v>39</v>
-      </c>
-      <c r="E156" t="n">
-        <v>41925.5</v>
-      </c>
-      <c r="F156" t="n">
-        <v>1031846.360978362</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="n">
-        <v>101</v>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>25-03</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="n">
-        <v>45717</v>
-      </c>
-      <c r="D157" t="n">
-        <v>56</v>
-      </c>
-      <c r="E157" t="n">
-        <v>61336.5</v>
-      </c>
-      <c r="F157" t="n">
-        <v>1019471.255091585</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="n">
-        <v>102</v>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>25-03</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="n">
-        <v>45717</v>
-      </c>
-      <c r="D158" t="n">
-        <v>73</v>
-      </c>
-      <c r="E158" t="n">
-        <v>76512.5</v>
-      </c>
-      <c r="F158" t="n">
-        <v>1027473.211804454</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="n">
-        <v>103</v>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>25-04</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="n">
-        <v>45748</v>
-      </c>
-      <c r="D159" t="n">
-        <v>48</v>
-      </c>
-      <c r="E159" t="n">
-        <v>52549</v>
-      </c>
-      <c r="F159" t="n">
-        <v>1007127.512720508</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="n">
-        <v>103</v>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>25-05</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="n">
-        <v>45778</v>
-      </c>
-      <c r="D160" t="n">
-        <v>27</v>
-      </c>
-      <c r="E160" t="n">
-        <v>27279.16666666667</v>
-      </c>
-      <c r="F160" t="n">
-        <v>1054682.526338781</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="n">
-        <v>104</v>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>25-05</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="n">
-        <v>45778</v>
-      </c>
-      <c r="D161" t="n">
-        <v>19</v>
-      </c>
-      <c r="E161" t="n">
-        <v>20657.66666666667</v>
-      </c>
-      <c r="F161" t="n">
-        <v>990012.6335985024</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="n">
-        <v>104</v>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>25-06</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="n">
-        <v>45809</v>
-      </c>
-      <c r="D162" t="n">
-        <v>123</v>
-      </c>
-      <c r="E162" t="n">
-        <v>134440.2</v>
-      </c>
-      <c r="F162" t="n">
-        <v>1024928.951634053</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="n">
-        <v>105</v>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>25-07</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="n">
-        <v>45839</v>
-      </c>
-      <c r="D163" t="n">
-        <v>133</v>
-      </c>
-      <c r="E163" t="n">
-        <v>141092.5</v>
-      </c>
-      <c r="F163" t="n">
-        <v>1043780.604139672</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="n">
-        <v>105</v>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>25-08</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="n">
-        <v>45870</v>
-      </c>
-      <c r="D164" t="n">
-        <v>62</v>
-      </c>
-      <c r="E164" t="n">
-        <v>66573</v>
-      </c>
-      <c r="F164" t="n">
-        <v>1022804.723592447</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="n">
-        <v>106</v>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>25-09</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="n">
-        <v>45901</v>
-      </c>
-      <c r="D165" t="n">
-        <v>146</v>
-      </c>
-      <c r="E165" t="n">
-        <v>155394</v>
-      </c>
-      <c r="F165" t="n">
-        <v>1022796.452305108</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="n">
-        <v>107</v>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>25-11</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="n">
-        <v>45962</v>
-      </c>
-      <c r="D166" t="n">
-        <v>71</v>
-      </c>
-      <c r="E166" t="n">
-        <v>75319</v>
-      </c>
-      <c r="F166" t="n">
         <v>1041406.212069111</v>
       </c>
     </row>

--- a/2-OI_a/Campagnes.xlsx
+++ b/2-OI_a/Campagnes.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F187"/>
+  <dimension ref="A1:F193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4556,6 +4556,138 @@
         <v>1030082.766275187</v>
       </c>
     </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>133</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>25-12</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="D188" t="n">
+        <v>92</v>
+      </c>
+      <c r="E188" t="n">
+        <v>101097</v>
+      </c>
+      <c r="F188" t="n">
+        <v>1032879.98036723</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>134</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>26-01</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="D189" t="n">
+        <v>96</v>
+      </c>
+      <c r="E189" t="n">
+        <v>103662</v>
+      </c>
+      <c r="F189" t="n">
+        <v>1030036.235250944</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>135</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>26-02</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="D190" t="n">
+        <v>90</v>
+      </c>
+      <c r="E190" t="n">
+        <v>95319</v>
+      </c>
+      <c r="F190" t="n">
+        <v>1040430.271573602</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>135</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>26-03</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D191" t="n">
+        <v>35</v>
+      </c>
+      <c r="E191" t="n">
+        <v>38127.5</v>
+      </c>
+      <c r="F191" t="n">
+        <v>1008007.930531331</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>136</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>26-03</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D192" t="n">
+        <v>54</v>
+      </c>
+      <c r="E192" t="n">
+        <v>58737.5</v>
+      </c>
+      <c r="F192" t="n">
+        <v>1017586.299830886</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>137</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>26-04</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="D193" t="n">
+        <v>20</v>
+      </c>
+      <c r="E193" t="n">
+        <v>22531.33333333333</v>
+      </c>
+      <c r="F193" t="n">
+        <v>1023115.844684994</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
